--- a/src/data/chamados_verificacao.xlsx
+++ b/src/data/chamados_verificacao.xlsx
@@ -471,11 +471,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -502,25 +502,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cliente_10</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -528,30 +528,30 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46025</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46025</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cliente_6</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46025</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -609,11 +609,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -621,30 +621,30 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46027</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cliente_8</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -683,30 +683,30 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46030</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -714,30 +714,30 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -745,21 +745,21 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46037</v>
+        <v>46033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -776,30 +776,30 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46037</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -838,16 +838,16 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cliente_30</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -857,11 +857,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -869,30 +869,30 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46040</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -900,30 +900,30 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46047</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -962,30 +962,30 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46050</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -993,30 +993,30 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46051</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46054</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1055,21 +1055,21 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46054</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1086,30 +1086,30 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46057</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1117,30 +1117,30 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46061</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1148,30 +1148,30 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46062</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cliente_9</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1179,30 +1179,30 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46062</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1210,16 +1210,16 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46063</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1229,11 +1229,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46064</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cliente_7</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cliente_9</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1291,11 +1291,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1303,30 +1303,30 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46067</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cliente_8</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46068</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1353,11 +1353,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1365,30 +1365,30 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46069</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1396,30 +1396,30 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46072</v>
+        <v>46060</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cliente_7</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46073</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1458,12 +1458,12 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46080</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1489,30 +1489,30 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46082</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cliente_29</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1520,21 +1520,21 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46084</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1551,30 +1551,30 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46086</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46088</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1613,12 +1613,12 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46093</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1644,30 +1644,30 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46095</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1675,30 +1675,30 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46097</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1706,30 +1706,30 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46098</v>
+        <v>46073</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1737,21 +1737,21 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46101</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1768,30 +1768,30 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46102</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1799,30 +1799,30 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46106</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46109</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46109</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46110</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1923,30 +1923,30 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46111</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1954,30 +1954,30 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46112</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1985,30 +1985,30 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46114</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cliente_25</t>
+          <t>cliente_9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46114</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cliente_23</t>
+          <t>cliente_29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2047,30 +2047,30 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46116</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cliente_30</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2078,30 +2078,30 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46117</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2109,30 +2109,30 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46120</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2140,12 +2140,12 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46122</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2154,16 +2154,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2171,30 +2171,30 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46122</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cliente_1</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2202,30 +2202,30 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46123</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46125</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46125</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2295,30 +2295,30 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46126</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2326,21 +2326,21 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46126</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46128</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2388,30 +2388,30 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46130</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cliente_3</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2419,30 +2419,30 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46132</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46136</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cliente_1</t>
+          <t>cliente_9</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46137</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46137</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2543,30 +2543,30 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46138</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>cliente_23</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2574,30 +2574,30 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46139</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2605,83 +2605,83 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46141</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cliente_21</t>
+          <t>cliente_30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_1</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46023</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>cliente_24</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_1</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46023</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2694,56 +2694,56 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_1</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46029</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>cliente_6</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_1</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46029</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46032</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2791,30 +2791,30 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46035</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2822,30 +2822,30 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46040</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46041</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>cliente_21</t>
+          <t>cliente_14</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2884,30 +2884,30 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46044</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2915,30 +2915,30 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46048</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>cliente_18</t>
+          <t>cliente_30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2946,30 +2946,30 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46049</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46051</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>cliente_6</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3008,30 +3008,30 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46052</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cliente_18</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3039,30 +3039,30 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46053</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3070,30 +3070,30 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46059</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>cliente_23</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3101,30 +3101,30 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46060</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3132,52 +3132,52 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46063</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>141</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cliente_22</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>maquina_6</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>avaliacao_do_equipamento</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
         <v>1</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>cliente_17</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>maquina_8</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>manutencao_corretiva</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>3</v>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>prioridade_2</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46063</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>cliente_21</t>
+          <t>cliente_2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3194,30 +3194,30 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46066</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3225,16 +3225,16 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46067</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>cliente_10</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3244,11 +3244,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3256,30 +3256,30 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46070</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_29</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3287,30 +3287,30 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46071</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3318,30 +3318,30 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46076</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46076</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_29</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3380,12 +3380,12 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46077</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3394,16 +3394,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>46079</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46079</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>cliente_30</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3473,30 +3473,30 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46079</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3504,30 +3504,30 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46080</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>cliente_7</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3535,30 +3535,30 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>46082</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46083</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_18</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3597,30 +3597,30 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46084</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>cliente_8</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3628,30 +3628,30 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>46085</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3659,16 +3659,16 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>46086</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46088</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>cliente_18</t>
+          <t>cliente_13</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3709,11 +3709,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3721,30 +3721,30 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46090</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3752,30 +3752,30 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46091</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3783,30 +3783,30 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46092</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3814,30 +3814,30 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>46092</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3845,16 +3845,16 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>46093</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>cliente_26</t>
+          <t>cliente_27</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3876,30 +3876,30 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>46093</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>cliente_29</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3907,12 +3907,12 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3938,30 +3938,30 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>46096</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3969,30 +3969,30 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46097</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cliente_24</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4031,21 +4031,21 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46097</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>cliente_3</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4062,16 +4062,16 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46097</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4093,16 +4093,16 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46098</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4112,11 +4112,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>46098</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cliente_9</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4143,11 +4143,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46099</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46102</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>cliente_26</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46102</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4248,30 +4248,30 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46104</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>cliente_3</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4279,21 +4279,21 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46105</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4310,30 +4310,30 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>46108</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4341,30 +4341,30 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46111</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4372,30 +4372,30 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46112</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4403,30 +4403,30 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46115</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>cliente_3</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4434,30 +4434,30 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46115</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cliente_24</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4465,30 +4465,30 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46117</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_29</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4496,21 +4496,21 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46118</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4527,30 +4527,30 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46120</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_9</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4558,21 +4558,21 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>46124</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_29</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4589,30 +4589,30 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>46125</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4620,30 +4620,30 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46128</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>187</v>
+        <v>9</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4651,16 +4651,16 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>cliente_7</t>
+          <t>cliente_25</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4678,118 +4678,118 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>46131</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46133</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>46135</v>
+        <v>46039</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>46135</v>
+        <v>46039</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4802,25 +4802,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>46138</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4833,189 +4833,189 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>46139</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>cliente_23</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46140</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>46141</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>46141</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>46141</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>cliente_23</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>prioridade_2</t>
+          <t>prioridade_3</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>46141</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_15</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5023,21 +5023,21 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>46023</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5054,30 +5054,30 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>46026</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>cliente_25</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>46027</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_7</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5116,21 +5116,21 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>46032</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>cliente_14</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5147,30 +5147,30 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>46035</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>cliente_3</t>
+          <t>cliente_8</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -5178,30 +5178,30 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>46035</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5209,21 +5209,21 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>46036</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>cliente_24</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>46037</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5271,30 +5271,30 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>46040</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_14</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>46040</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>cliente_6</t>
+          <t>cliente_13</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5333,30 +5333,30 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>46040</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -5364,21 +5364,21 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>46041</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5395,16 +5395,16 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>46042</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>cliente_12</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5414,11 +5414,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -5426,16 +5426,16 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>46044</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5445,11 +5445,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>46045</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>cliente_27</t>
+          <t>cliente_6</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>46048</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5507,11 +5507,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -5519,30 +5519,30 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>46050</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -5550,30 +5550,30 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>46052</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>177</v>
+        <v>12</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>cliente_16</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5581,30 +5581,30 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>46054</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_18</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5612,30 +5612,30 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>46059</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_17</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5643,30 +5643,30 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>46060</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5674,30 +5674,30 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>46064</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>cliente_8</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5705,21 +5705,21 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>46065</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5736,30 +5736,30 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>46066</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>cliente_7</t>
+          <t>cliente_26</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>46070</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_9</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5798,30 +5798,30 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>46071</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>cliente_22</t>
+          <t>cliente_1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>maquina_5</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5829,16 +5829,16 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>46074</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>cliente_2</t>
+          <t>cliente_4</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5860,30 +5860,30 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>46075</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>cliente_30</t>
+          <t>cliente_27</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_9</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -5891,30 +5891,30 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>46077</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_28</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -5922,21 +5922,21 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>46078</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5953,30 +5953,30 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>46081</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>cliente_19</t>
+          <t>cliente_11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -5984,30 +5984,30 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>46084</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6015,30 +6015,30 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>46084</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>161</v>
+        <v>36</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>cliente_30</t>
+          <t>cliente_25</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6046,30 +6046,30 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>46085</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>cliente_25</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6077,30 +6077,30 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>46090</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>cliente_9</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6108,16 +6108,16 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>46095</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>cliente_11</t>
+          <t>cliente_19</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6127,11 +6127,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6139,16 +6139,16 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>46096</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>cliente_15</t>
+          <t>cliente_22</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6158,11 +6158,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>46098</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>cliente_29</t>
+          <t>cliente_21</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6189,11 +6189,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -6201,21 +6201,21 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>46098</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>cliente_29</t>
+          <t>cliente_5</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>maquina_1</t>
+          <t>maquina_8</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6232,21 +6232,21 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>46105</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>cliente_17</t>
+          <t>cliente_10</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6263,30 +6263,30 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>46109</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_4</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -6294,16 +6294,16 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>46111</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>cliente_9</t>
+          <t>cliente_25</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>cliente_26</t>
+          <t>cliente_23</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6356,30 +6356,30 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>46119</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>cliente_4</t>
+          <t>cliente_9</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>cliente_28</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6418,30 +6418,30 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>46121</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>cliente_13</t>
+          <t>cliente_20</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>maquina_4</t>
+          <t>maquina_10</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -6449,30 +6449,30 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>46123</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>cliente_20</t>
+          <t>cliente_12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>maquina_10</t>
+          <t>maquina_7</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -6480,30 +6480,30 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>46123</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>cliente_21</t>
+          <t>cliente_24</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>maquina_9</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>avaliacao_do_equipamento</t>
+          <t>manutencao_preventiva</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -6511,12 +6511,12 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>46124</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>maquina_6</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>46126</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>cliente_6</t>
+          <t>cliente_13</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>maquina_3</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -6573,30 +6573,30 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>46126</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cliente_5</t>
+          <t>cliente_16</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>maquina_8</t>
+          <t>maquina_3</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>manutencao_preventiva</t>
+          <t>manutencao_corretiva</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -6604,12 +6604,12 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>46130</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>maquina_7</t>
+          <t>maquina_1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="201">
@@ -6644,21 +6644,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>cliente_1</t>
+          <t>cliente_13</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>maquina_2</t>
+          <t>maquina_6</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>manutencao_corretiva</t>
+          <t>avaliacao_do_equipamento</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
     </row>
   </sheetData>
